--- a/data/trans_bre/P38A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,98</t>
+          <t>-4,59; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 17,56</t>
+          <t>3,8; 17,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 12,5</t>
+          <t>0,79; 11,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 7,1</t>
+          <t>-5,17; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 24,93</t>
+          <t>4,92; 25,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 14,43</t>
+          <t>0,85; 13,73</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,09</t>
+          <t>1,55; 9,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,52</t>
+          <t>2,79; 10,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 10,27</t>
+          <t>-1,15; 10,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 12,19</t>
+          <t>1,79; 11,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,41</t>
+          <t>3,11; 12,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 12,44</t>
+          <t>-1,24; 12,6</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,13</t>
+          <t>-0,68; 8,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 7,27</t>
+          <t>-1,33; 7,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,06</t>
+          <t>0,35; 7,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,41</t>
+          <t>-0,74; 9,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 8,36</t>
+          <t>-1,42; 8,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,91</t>
+          <t>0,37; 8,9</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,58</t>
+          <t>2,74; 13,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,75</t>
+          <t>-3,04; 4,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 6,94</t>
+          <t>-40,22; 6,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 17,4</t>
+          <t>3,27; 17,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,36</t>
+          <t>-3,21; 5,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 7,91</t>
+          <t>-43,59; 7,59</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,16</t>
+          <t>1,23; 12,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,85</t>
+          <t>4,64; 17,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 12,86</t>
+          <t>-1,23; 13,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 15,98</t>
+          <t>1,38; 15,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 25,73</t>
+          <t>5,48; 24,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 16,52</t>
+          <t>-1,38; 16,92</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 8,24</t>
+          <t>-0,87; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,19</t>
+          <t>1,31; 12,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,76</t>
+          <t>-1,6; 6,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 9,45</t>
+          <t>-0,92; 9,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,94</t>
+          <t>1,44; 15,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,43</t>
+          <t>-1,64; 6,73</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,0</t>
+          <t>0,59; 6,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,35</t>
+          <t>2,69; 12,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,95</t>
+          <t>4,8; 16,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,0</t>
+          <t>0,65; 7,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 17,68</t>
+          <t>3,64; 17,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 20,82</t>
+          <t>5,48; 21,13</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,49</t>
+          <t>-0,73; 7,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,67</t>
+          <t>3,03; 8,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 52,37</t>
+          <t>6,87; 52,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,77</t>
+          <t>-0,89; 10,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,05</t>
+          <t>3,36; 9,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 242,18</t>
+          <t>10,6; 246,0</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,03</t>
+          <t>2,69; 6,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,97</t>
+          <t>4,72; 8,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 28,77</t>
+          <t>3,27; 28,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,16</t>
+          <t>3,12; 7,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,68</t>
+          <t>5,59; 9,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,91; 46,0</t>
+          <t>3,87; 47,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,04</t>
+          <t>-5,21; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 17,37</t>
+          <t>4,03; 17,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 11,8</t>
+          <t>-0,59; 6,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 8,61</t>
+          <t>-5,8; 7,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 25,1</t>
+          <t>4,93; 25,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 13,73</t>
+          <t>-0,61; 6,65</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,59</t>
+          <t>1,9; 9,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,38</t>
+          <t>2,82; 10,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 10,24</t>
+          <t>-1,39; 8,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 11,45</t>
+          <t>2,15; 11,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,45</t>
+          <t>3,19; 12,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 12,6</t>
+          <t>-1,62; 10,61</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,2</t>
+          <t>-0,34; 8,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,28</t>
+          <t>-1,06; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,97</t>
+          <t>0,47; 7,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 9,61</t>
+          <t>-0,43; 9,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,47</t>
+          <t>-1,15; 8,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,9</t>
+          <t>0,5; 8,94</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,12</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,16%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 13,64</t>
+          <t>3,35; 14,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,54</t>
+          <t>-2,82; 5,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 6,8</t>
+          <t>-0,39; 13,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 17,82</t>
+          <t>4,18; 18,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,01</t>
+          <t>-2,98; 5,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 7,59</t>
+          <t>-0,41; 15,89</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>7,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,85</t>
+          <t>0,86; 12,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 17,82</t>
+          <t>4,93; 18,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 13,12</t>
+          <t>0,96; 14,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 15,44</t>
+          <t>0,96; 15,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 24,05</t>
+          <t>5,93; 24,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 16,92</t>
+          <t>1,17; 19,39</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 8,12</t>
+          <t>-0,27; 8,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,39</t>
+          <t>1,47; 12,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,18</t>
+          <t>-0,14; 7,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,16</t>
+          <t>-0,29; 9,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 15,08</t>
+          <t>1,79; 15,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 6,73</t>
+          <t>-0,09; 8,58</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,83</t>
+          <t>0,5; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,04</t>
+          <t>2,55; 11,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,71</t>
+          <t>2,8; 10,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,79</t>
+          <t>0,57; 8,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 17,63</t>
+          <t>3,42; 17,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 21,13</t>
+          <t>3,28; 12,86</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,75</t>
+          <t>8,78</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,89</t>
+          <t>-0,62; 7,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,37</t>
+          <t>2,86; 8,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 52,56</t>
+          <t>3,83; 13,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 10,37</t>
+          <t>-0,76; 9,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,73</t>
+          <t>3,16; 9,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 246,0</t>
+          <t>5,73; 22,6</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,04</t>
+          <t>2,72; 5,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,12</t>
+          <t>4,54; 7,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 28,16</t>
+          <t>3,9; 7,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,16</t>
+          <t>3,12; 6,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,86</t>
+          <t>5,38; 9,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,87; 47,1</t>
+          <t>4,65; 9,71</t>
         </is>
       </c>
     </row>
